--- a/services/integrator/internal/document/testdata/kartu-stok-2025.golden.xlsx
+++ b/services/integrator/internal/document/testdata/kartu-stok-2025.golden.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Catatan: 11 barang tanpa saldo awal dan tanpa mutasi tidak ditampilkan.</t>
+    <t xml:space="preserve">Catatan: 12 barang tanpa saldo awal dan tanpa mutasi tidak ditampilkan.</t>
   </si>
 </sst>
 </file>
